--- a/configs/config_g3p3_b0.xlsx
+++ b/configs/config_g3p3_b0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nrel-my.sharepoint.com/personal/sletizia_nrel_gov/Documents/Desktop/Main/G3P3/g3p3_lidar_processing/configs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aabraha2\Documents\G3P3\Codes\g3p3_lidar_processing\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{04294DC9-DB31-448F-BB95-920AF215A499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5855D667-D7B5-43CC-92CA-32DBFFC6CA7E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE379BB-F87D-462F-B9CF-93380031467D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="18552" windowHeight="10488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -179,7 +179,7 @@
     <t>roof.lidar.z01.a0.\d{8}.\d{1}(?:030|110|150|230|310|350|430|510|550|630|710|750|830|910|950|)\d{2}.user5.nc</t>
   </si>
   <si>
-    <t>3.points</t>
+    <t>4.points</t>
   </si>
 </sst>
 </file>
@@ -357,10 +357,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -788,7 +784,7 @@
         <v>20250416</v>
       </c>
       <c r="L3" s="22">
-        <v>20250416</v>
+        <v>20250430</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -824,13 +820,13 @@
         <v>20250416</v>
       </c>
       <c r="J4" s="22">
-        <v>20250430</v>
+        <v>20250601</v>
       </c>
       <c r="K4" s="22">
-        <v>20250430</v>
+        <v>20250601</v>
       </c>
       <c r="L4" s="22">
-        <v>20250430</v>
+        <v>20250601</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -956,7 +952,7 @@
         <v>-0.1</v>
       </c>
       <c r="L7" s="7">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -1040,7 +1036,7 @@
         <v>-0.1</v>
       </c>
       <c r="L9" s="7">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1082,7 +1078,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="7">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -1586,7 +1582,7 @@
         <v>0.1</v>
       </c>
       <c r="L22" s="24">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>

--- a/configs/config_g3p3_b0.xlsx
+++ b/configs/config_g3p3_b0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aabraha2\Documents\G3P3\Codes\g3p3_lidar_processing\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE379BB-F87D-462F-B9CF-93380031467D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBF86CA-D99C-454B-9730-488460033AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="18552" windowHeight="10488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>name</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>4.points</t>
+  </si>
+  <si>
+    <t>g3p3.lidar.z01.a0.\d{8}.\d{6}.stare.nc</t>
+  </si>
+  <si>
+    <t>stare</t>
   </si>
 </sst>
 </file>
@@ -265,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -341,6 +347,9 @@
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -648,25 +657,25 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.5546875" style="21" customWidth="1"/>
-    <col min="4" max="5" width="55.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.5703125" style="21" customWidth="1"/>
+    <col min="4" max="5" width="55.42578125" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="58" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.5546875" style="21" customWidth="1"/>
-    <col min="8" max="9" width="55.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="51.44140625" style="4" customWidth="1"/>
-    <col min="11" max="12" width="48.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="57.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.5703125" style="21" customWidth="1"/>
+    <col min="8" max="9" width="55.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="51.42578125" style="4" customWidth="1"/>
+    <col min="11" max="12" width="48.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="57.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="53" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.77734375" style="4"/>
+    <col min="16" max="16" width="47.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -703,11 +712,13 @@
       <c r="L1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="3"/>
+      <c r="M1" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
@@ -744,12 +755,14 @@
       <c r="L2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
@@ -786,12 +799,14 @@
       <c r="L3" s="22">
         <v>20250430</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="26">
+        <v>20250506</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -828,12 +843,14 @@
       <c r="L4" s="22">
         <v>20250601</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="M4" s="26">
+        <v>20250507</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,12 +887,14 @@
       <c r="L5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -912,12 +931,14 @@
       <c r="L6" s="5">
         <v>0</v>
       </c>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
@@ -954,12 +975,14 @@
       <c r="L7" s="7">
         <v>0.4</v>
       </c>
-      <c r="M7" s="7"/>
+      <c r="M7" s="7">
+        <v>-0.1</v>
+      </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>3</v>
       </c>
@@ -996,12 +1019,14 @@
       <c r="L8" s="7">
         <v>1.6</v>
       </c>
-      <c r="M8" s="7"/>
+      <c r="M8" s="7">
+        <v>0.1</v>
+      </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
@@ -1038,12 +1063,14 @@
       <c r="L9" s="7">
         <v>-1.2</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7">
+        <v>-0.1</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="1:16" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>5</v>
       </c>
@@ -1080,12 +1107,14 @@
       <c r="L10" s="7">
         <v>1.2</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7">
+        <v>0.1</v>
+      </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:16" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>6</v>
       </c>
@@ -1122,12 +1151,14 @@
       <c r="L11" s="10">
         <v>0.1</v>
       </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="10">
+        <v>0.25</v>
+      </c>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:16" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" s="11" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>7</v>
       </c>
@@ -1164,12 +1195,14 @@
       <c r="L12" s="10">
         <v>0.1</v>
       </c>
-      <c r="M12" s="10"/>
+      <c r="M12" s="10">
+        <v>0.1</v>
+      </c>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="1:16" s="14" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" s="14" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>8</v>
       </c>
@@ -1206,12 +1239,14 @@
       <c r="L13" s="13">
         <v>2</v>
       </c>
-      <c r="M13" s="13"/>
+      <c r="M13" s="13">
+        <v>0.01</v>
+      </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
     </row>
-    <row r="14" spans="1:16" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>9</v>
       </c>
@@ -1248,12 +1283,14 @@
       <c r="L14" s="16">
         <v>200</v>
       </c>
-      <c r="M14" s="16"/>
+      <c r="M14" s="16">
+        <v>200</v>
+      </c>
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
     </row>
-    <row r="15" spans="1:16" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>10</v>
       </c>
@@ -1290,12 +1327,14 @@
       <c r="L15" s="16">
         <v>200</v>
       </c>
-      <c r="M15" s="16"/>
+      <c r="M15" s="16">
+        <v>200</v>
+      </c>
       <c r="N15" s="16"/>
       <c r="O15" s="16"/>
       <c r="P15" s="16"/>
     </row>
-    <row r="16" spans="1:16" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>11</v>
       </c>
@@ -1332,12 +1371,14 @@
       <c r="L16" s="16">
         <v>50</v>
       </c>
-      <c r="M16" s="16"/>
+      <c r="M16" s="16">
+        <v>50</v>
+      </c>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
     </row>
-    <row r="17" spans="1:27" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" s="17" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>12</v>
       </c>
@@ -1374,12 +1415,14 @@
       <c r="L17" s="16">
         <v>600</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="16">
+        <v>600</v>
+      </c>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
       <c r="P17" s="16"/>
     </row>
-    <row r="18" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1416,12 +1459,14 @@
       <c r="L18" s="23">
         <v>96</v>
       </c>
-      <c r="M18" s="5"/>
+      <c r="M18" s="23">
+        <v>50</v>
+      </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
     </row>
-    <row r="19" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1458,12 +1503,14 @@
       <c r="L19" s="23">
         <v>1000</v>
       </c>
-      <c r="M19" s="5"/>
+      <c r="M19" s="23">
+        <v>300</v>
+      </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
     </row>
-    <row r="20" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1500,12 +1547,14 @@
       <c r="L20" s="23">
         <v>-25</v>
       </c>
-      <c r="M20" s="5"/>
+      <c r="M20" s="23">
+        <v>-25</v>
+      </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -1542,12 +1591,14 @@
       <c r="L21" s="23">
         <v>50</v>
       </c>
-      <c r="M21" s="5"/>
+      <c r="M21" s="23">
+        <v>50</v>
+      </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
     </row>
-    <row r="22" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -1584,7 +1635,9 @@
       <c r="L22" s="24">
         <v>1E-4</v>
       </c>
-      <c r="M22" s="13"/>
+      <c r="M22" s="24">
+        <v>1E-4</v>
+      </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -1600,7 +1653,7 @@
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
     </row>
-    <row r="23" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
@@ -1637,12 +1690,14 @@
       <c r="L23" s="23">
         <v>30</v>
       </c>
-      <c r="M23" s="5"/>
+      <c r="M23" s="23">
+        <v>30</v>
+      </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
     </row>
-    <row r="24" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1679,12 +1734,14 @@
       <c r="L24" s="23">
         <v>20</v>
       </c>
-      <c r="M24" s="5"/>
+      <c r="M24" s="23">
+        <v>20</v>
+      </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
     </row>
-    <row r="25" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -1721,12 +1778,14 @@
       <c r="L25" s="23">
         <v>1</v>
       </c>
-      <c r="M25" s="5"/>
+      <c r="M25" s="23">
+        <v>1</v>
+      </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
     </row>
-    <row r="26" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -1763,12 +1822,14 @@
       <c r="L26" s="23">
         <v>1</v>
       </c>
-      <c r="M26" s="5"/>
+      <c r="M26" s="23">
+        <v>1</v>
+      </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
     </row>
-    <row r="27" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -1805,12 +1866,14 @@
       <c r="L27" s="23">
         <v>30</v>
       </c>
-      <c r="M27" s="5"/>
+      <c r="M27" s="23">
+        <v>30</v>
+      </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
     </row>
-    <row r="28" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
@@ -1847,12 +1910,14 @@
       <c r="L28" s="25">
         <v>0.5</v>
       </c>
-      <c r="M28" s="10"/>
+      <c r="M28" s="25">
+        <v>0.5</v>
+      </c>
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" spans="1:27" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>22</v>
       </c>
@@ -1889,12 +1954,14 @@
       <c r="L29" s="16">
         <v>25</v>
       </c>
-      <c r="M29" s="16"/>
+      <c r="M29" s="16">
+        <v>25</v>
+      </c>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
     </row>
-    <row r="30" spans="1:27" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>23</v>
       </c>
@@ -1931,12 +1998,14 @@
       <c r="L30" s="16">
         <v>1</v>
       </c>
-      <c r="M30" s="16"/>
+      <c r="M30" s="16">
+        <v>1</v>
+      </c>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
     </row>
-    <row r="31" spans="1:27" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" s="17" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>24</v>
       </c>
@@ -1973,12 +2042,14 @@
       <c r="L31" s="16">
         <v>99</v>
       </c>
-      <c r="M31" s="16"/>
+      <c r="M31" s="16">
+        <v>99</v>
+      </c>
       <c r="N31" s="16"/>
       <c r="O31" s="16"/>
       <c r="P31" s="16"/>
     </row>
-    <row r="32" spans="1:27" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>25</v>
       </c>
@@ -2015,12 +2086,14 @@
       <c r="L32" s="19">
         <v>1E-4</v>
       </c>
-      <c r="M32" s="19"/>
+      <c r="M32" s="19">
+        <v>1E-4</v>
+      </c>
       <c r="N32" s="19"/>
       <c r="O32" s="19"/>
       <c r="P32" s="19"/>
     </row>
-    <row r="33" spans="1:16" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" s="20" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>26</v>
       </c>
@@ -2057,12 +2130,14 @@
       <c r="L33" s="19">
         <v>0.1</v>
       </c>
-      <c r="M33" s="19"/>
+      <c r="M33" s="19">
+        <v>0.1</v>
+      </c>
       <c r="N33" s="19"/>
       <c r="O33" s="19"/>
       <c r="P33" s="19"/>
     </row>
-    <row r="34" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>27</v>
       </c>
@@ -2099,12 +2174,14 @@
       <c r="L34" s="7">
         <v>0.25</v>
       </c>
-      <c r="M34" s="7"/>
+      <c r="M34" s="7">
+        <v>0.25</v>
+      </c>
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
     </row>
-    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>28</v>
       </c>
@@ -2141,12 +2218,14 @@
       <c r="L35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M35" s="3"/>
+      <c r="M35" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
@@ -2183,12 +2262,14 @@
       <c r="L36" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M36" s="3"/>
+      <c r="M36" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
@@ -2225,7 +2306,9 @@
       <c r="L37" s="5">
         <v>-30</v>
       </c>
-      <c r="M37" s="5"/>
+      <c r="M37" s="5">
+        <v>0</v>
+      </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
